--- a/daily_matches/job_matches_2026-05-24.xlsx
+++ b/daily_matches/job_matches_2026-05-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Azure DevOps Cloud &amp; Infrastructure Engineer</t>
+          <t>Senior AI/ML Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Milford, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Kubernetes, AKS, CI/CD, GitHub Actions, Terraform, Git, SQL, R</t>
+          <t>Generative AI, RAG, TensorFlow, PyTorch, Azure ML, MLflow, Docker, Kubernetes, Databricks, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,147 +496,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09464e604326699d</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Service Management Team Engineer</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>S&amp;P Global</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, Git, PostgreSQL, MySQL, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e9e33a142f9ff07f</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Roku</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Paramount</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Burbank, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>RAG, Copilot, Docker, CI/CD, Jenkins, Git, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b147475a72f946d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Forward Deployment AI Engineer</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Lyra Technology Group</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>San Diego, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>10</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, LangChain, RAG, Gemini, Pinecone, Prompt Engineering, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6737f847c2ce6606</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - AI</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Acuity Inc.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, FastAPI, Kubernetes, CI/CD, NoSQL, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-05-23</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=284d6615dd0a33f5</t>
+          <t>https://www.indeed.com/viewjob?jk=16f0b949e7e7036a</t>
         </is>
       </c>
     </row>
